--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Llama-3.1-8B-Instruct/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Llama-3.1-8B-Instruct/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.25</v>
+        <v>0.3461538461538461</v>
       </c>
       <c r="B2">
-        <v>0.25</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="C2">
-        <v>0.3333333333333333</v>
+        <v>0.3857142857142857</v>
       </c>
       <c r="D2">
-        <v>0.75</v>
+        <v>0.6991869918699187</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>104</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Llama-3.1-8B-Instruct/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Llama-3.1-8B-Instruct/metrics_default_vs_simple.xlsx
@@ -420,22 +420,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.3461538461538461</v>
+        <v>0.404040404040404</v>
       </c>
       <c r="B2">
-        <v>0.05263157894736842</v>
+        <v>0.04761904761904762</v>
       </c>
       <c r="C2">
-        <v>0.3857142857142857</v>
+        <v>0.4233576642335766</v>
       </c>
       <c r="D2">
-        <v>0.6991869918699187</v>
+        <v>0.6583333333333333</v>
       </c>
       <c r="E2">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="F2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G2">
         <v>17</v>
